--- a/artfynd/A 14955-2025 artfynd.xlsx
+++ b/artfynd/A 14955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108200</v>
       </c>
       <c r="B2" t="n">
-        <v>99054</v>
+        <v>99055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108258</v>
       </c>
       <c r="B3" t="n">
-        <v>92272</v>
+        <v>92273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>131108302</v>
       </c>
       <c r="B4" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14955-2025 artfynd.xlsx
+++ b/artfynd/A 14955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108200</v>
       </c>
       <c r="B2" t="n">
-        <v>99055</v>
+        <v>99057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108258</v>
       </c>
       <c r="B3" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>131108302</v>
       </c>
       <c r="B4" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14955-2025 artfynd.xlsx
+++ b/artfynd/A 14955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108200</v>
       </c>
       <c r="B2" t="n">
-        <v>99057</v>
+        <v>99058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108258</v>
       </c>
       <c r="B3" t="n">
-        <v>92275</v>
+        <v>92276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>131108302</v>
       </c>
       <c r="B4" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14955-2025 artfynd.xlsx
+++ b/artfynd/A 14955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108200</v>
       </c>
       <c r="B2" t="n">
-        <v>99058</v>
+        <v>99059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108258</v>
       </c>
       <c r="B3" t="n">
-        <v>92276</v>
+        <v>92277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>131108302</v>
       </c>
       <c r="B4" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14955-2025 artfynd.xlsx
+++ b/artfynd/A 14955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108200</v>
       </c>
       <c r="B2" t="n">
-        <v>99059</v>
+        <v>99062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108258</v>
       </c>
       <c r="B3" t="n">
-        <v>92277</v>
+        <v>92280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>131108302</v>
       </c>
       <c r="B4" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14955-2025 artfynd.xlsx
+++ b/artfynd/A 14955-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131108200</v>
       </c>
       <c r="B2" t="n">
-        <v>99062</v>
+        <v>99063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>131108258</v>
       </c>
       <c r="B3" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         <v>131108302</v>
       </c>
       <c r="B4" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14955-2025 artfynd.xlsx
+++ b/artfynd/A 14955-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131108200</v>
+        <v>131108302</v>
       </c>
       <c r="B2" t="n">
-        <v>99063</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616710</v>
+        <v>616707</v>
       </c>
       <c r="R2" t="n">
-        <v>6934282</v>
+        <v>6934308</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2025-0751</t>
+          <t>2025-0755</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,11 +803,11 @@
         <v>131108258</v>
       </c>
       <c r="B3" t="n">
-        <v>92281</v>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -930,54 +930,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131108302</v>
+        <v>131108287</v>
       </c>
       <c r="B4" t="n">
-        <v>91822</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Patronssvedberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616707</v>
+        <v>616684</v>
       </c>
       <c r="R4" t="n">
-        <v>6934308</v>
+        <v>6934160</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,27 +995,32 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025-0755</t>
+          <t>2025-0158</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosöksspår på död tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1040,381 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131108230</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Patronssvedberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>616647</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6934200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2025-0160</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal spillning</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131108160</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Patronssvedberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>616687</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6934322</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2025-0749</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131108200</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Patronssvedberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>616710</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6934282</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2025-0751</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 14955-2025 artfynd.xlsx
+++ b/artfynd/A 14955-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108302</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108258</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108287</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,6 +1189,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108230</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1294,6 +1319,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108160</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1419,8 +1449,21 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131108200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>